--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260702.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260702.xlsx
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>15,866,648</t>
+          <t>9,865,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>9,865,000</t>
+          <t>15,866,648</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>2,114,000</t>
+          <t>3,863,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>3,863,000</t>
+          <t>2,114,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
